--- a/templates/svodnaya_template.xlsx
+++ b/templates/svodnaya_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\centrcom\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEECAC0B-26A7-4E29-8078-BC604F884A24}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1387F0B7-C696-4233-A1B3-9F8E53A4ED49}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,27 +57,9 @@
     <t>Оценка за сборы</t>
   </si>
   <si>
-    <t xml:space="preserve"> выбор места для стрельбы, </t>
-  </si>
-  <si>
-    <t>передвижение на поле боя перебежками</t>
-  </si>
-  <si>
-    <t>передвижение на поле боя переползанием</t>
-  </si>
-  <si>
-    <t>итоговая</t>
-  </si>
-  <si>
-    <t>неполная разборка – сборка автомата Калашникова </t>
-  </si>
-  <si>
     <t>Выполнение начального упражнения стрельбы</t>
   </si>
   <si>
-    <t>первое упражнение по метанию ручной гранаты </t>
-  </si>
-  <si>
     <t>Кросс (3 км.) </t>
   </si>
   <si>
@@ -90,30 +72,6 @@
     <t>Прыжки в длину с места</t>
   </si>
   <si>
-    <t>строевая стойка</t>
-  </si>
-  <si>
-    <t>повороты на месте и в движении</t>
-  </si>
-  <si>
-    <t>строевой шаг, воинское приветствие</t>
-  </si>
-  <si>
-    <t>остановка кровотечения</t>
-  </si>
-  <si>
-    <t>наложение повязки на раны</t>
-  </si>
-  <si>
-    <t>действия солдата по сигналам оповещения</t>
-  </si>
-  <si>
-    <t>выполнение нормативов одевания  СИЗ</t>
-  </si>
-  <si>
-    <t>преодоление  заражённого участка местности</t>
-  </si>
-  <si>
     <t>оценочная ведомость учащихся {{SCHOOL_NAME}}</t>
   </si>
   <si>
@@ -139,13 +97,55 @@
   </si>
   <si>
     <t xml:space="preserve">                                                                                 м.п.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выбор места для стрельбы, </t>
+  </si>
+  <si>
+    <t>Передвижение на поле боя перебежками</t>
+  </si>
+  <si>
+    <t>Передвижение на поле боя переползанием</t>
+  </si>
+  <si>
+    <t>Итоговая</t>
+  </si>
+  <si>
+    <t>Неполная разборка – сборка автомата Калашникова </t>
+  </si>
+  <si>
+    <t>Первое упражнение по метанию ручной гранаты </t>
+  </si>
+  <si>
+    <t>Строевая стойка</t>
+  </si>
+  <si>
+    <t>Повороты на месте и в движении</t>
+  </si>
+  <si>
+    <t>Строевой шаг, воинское приветствие</t>
+  </si>
+  <si>
+    <t>Остановка кровотечения</t>
+  </si>
+  <si>
+    <t>Наложение повязки на раны</t>
+  </si>
+  <si>
+    <t>Действия солдата по сигналам оповещения</t>
+  </si>
+  <si>
+    <t>Выполнение нормативов одевания  СИЗ</t>
+  </si>
+  <si>
+    <t>Преодоление  заражённого участка местности</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,7 +161,8 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -169,7 +170,15 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -310,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,29 +337,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -361,7 +349,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -651,11 +666,17 @@
     <col min="2" max="2" width="18" style="4" customWidth="1"/>
     <col min="3" max="4" width="4.7109375" style="4" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" style="1" customWidth="1"/>
-    <col min="6" max="27" width="4.7109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" style="4" customWidth="1"/>
+    <col min="9" max="23" width="4.7109375" style="4" customWidth="1"/>
+    <col min="24" max="24" width="4.5703125" style="4" customWidth="1"/>
+    <col min="25" max="26" width="4.7109375" style="4" customWidth="1"/>
+    <col min="27" max="27" width="5.5703125" style="4" customWidth="1"/>
     <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -666,7 +687,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1"/>
@@ -685,7 +706,7 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -696,8 +717,8 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="18" t="s">
-        <v>29</v>
+      <c r="L2" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -715,7 +736,7 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -726,8 +747,8 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="18" t="s">
-        <v>30</v>
+      <c r="L3" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -746,155 +767,155 @@
       <c r="AA3" s="1"/>
     </row>
     <row r="5" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="7" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="7" t="s">
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="7" t="s">
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="7" t="s">
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="U5" s="8"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="7" t="s">
+      <c r="U5" s="13"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="13" t="s">
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="14"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="18"/>
+      <c r="AA6" s="19"/>
     </row>
     <row r="7" spans="1:27" ht="206.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="I7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="L7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="M7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="N7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>13</v>
+      <c r="O7" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="U7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="V7" s="6" t="s">
-        <v>13</v>
+        <v>34</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="X7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z7" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="Y7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="AA7" s="5"/>
     </row>
@@ -914,7 +935,7 @@
       <c r="E8" s="3">
         <v>5</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="20">
         <v>6</v>
       </c>
       <c r="G8" s="3">
@@ -926,7 +947,7 @@
       <c r="I8" s="3">
         <v>9</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="20">
         <v>10</v>
       </c>
       <c r="K8" s="3">
@@ -941,7 +962,7 @@
       <c r="N8" s="3">
         <v>14</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="20">
         <v>15</v>
       </c>
       <c r="P8" s="3">
@@ -953,7 +974,7 @@
       <c r="R8" s="3">
         <v>18</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="20">
         <v>19</v>
       </c>
       <c r="T8" s="3">
@@ -962,7 +983,7 @@
       <c r="U8" s="3">
         <v>21</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V8" s="20">
         <v>22</v>
       </c>
       <c r="W8" s="3">
@@ -974,44 +995,44 @@
       <c r="Y8" s="3">
         <v>25</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="20">
         <v>26</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="20">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
